--- a/public/personListTemplate-en.xlsx
+++ b/public/personListTemplate-en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\v\log-lottery\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Frank/develop/log-lottery/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CB735B-E814-4B47-8E60-2A2FEB8F4CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75129140-A4EA-7349-A5D5-C2A9669DD9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3060" yWindow="4460" windowWidth="21600" windowHeight="11300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="152">
   <si>
     <t>uid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -473,13 +473,29 @@
   </si>
   <si>
     <t>Khaleesi</t>
+  </si>
+  <si>
+    <t>phoneNumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13000001300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13000001301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13000001302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,7 +592,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -859,17 +875,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="8.625" style="2"/>
+    <col min="1" max="1" width="14.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="38" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -882,8 +899,11 @@
       <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
         <v>39</v>
       </c>
@@ -896,8 +916,11 @@
       <c r="D2" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -910,8 +933,11 @@
       <c r="D3" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -924,8 +950,11 @@
       <c r="D4" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -938,8 +967,11 @@
       <c r="D5" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
@@ -952,8 +984,11 @@
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -966,8 +1001,11 @@
       <c r="D7" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
@@ -980,8 +1018,11 @@
       <c r="D8" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
@@ -994,8 +1035,11 @@
       <c r="D9" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1052,11 @@
       <c r="D10" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1022,8 +1069,11 @@
       <c r="D11" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
@@ -1036,8 +1086,11 @@
       <c r="D12" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
@@ -1050,8 +1103,11 @@
       <c r="D13" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
@@ -1064,8 +1120,11 @@
       <c r="D14" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
@@ -1078,8 +1137,11 @@
       <c r="D15" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
@@ -1092,8 +1154,11 @@
       <c r="D16" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
@@ -1106,8 +1171,11 @@
       <c r="D17" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
@@ -1120,8 +1188,11 @@
       <c r="D18" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
@@ -1134,8 +1205,11 @@
       <c r="D19" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
@@ -1148,8 +1222,11 @@
       <c r="D20" s="6" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
@@ -1162,8 +1239,11 @@
       <c r="D21" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1176,8 +1256,11 @@
       <c r="D22" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
@@ -1190,8 +1273,11 @@
       <c r="D23" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
@@ -1204,8 +1290,11 @@
       <c r="D24" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
@@ -1218,8 +1307,11 @@
       <c r="D25" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -1232,8 +1324,11 @@
       <c r="D26" s="6" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
@@ -1246,8 +1341,11 @@
       <c r="D27" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -1260,8 +1358,11 @@
       <c r="D28" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
@@ -1274,8 +1375,11 @@
       <c r="D29" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
@@ -1288,8 +1392,11 @@
       <c r="D30" s="6" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
         <v>31</v>
       </c>
@@ -1302,8 +1409,11 @@
       <c r="D31" s="6" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
@@ -1316,8 +1426,11 @@
       <c r="D32" s="6" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
@@ -1330,8 +1443,11 @@
       <c r="D33" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
@@ -1344,8 +1460,11 @@
       <c r="D34" s="6" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
@@ -1358,8 +1477,11 @@
       <c r="D35" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
@@ -1372,8 +1494,11 @@
       <c r="D36" s="6" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
@@ -1385,6 +1510,9 @@
       </c>
       <c r="D37" s="6" t="s">
         <v>147</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
